--- a/map/DC_Province.xlsx
+++ b/map/DC_Province.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2c7edca7daaa657/Image/Hình ảnh/ThanhPhat_Masan/DC FMCG/org/map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{69D89A4B-C117-4522-9C42-D6F8D84E04A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDADFA2B-4440-48A8-8F7C-F049E36735A1}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{69D89A4B-C117-4522-9C42-D6F8D84E04A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6D9D1FD-F9CC-440E-B1A3-6E7E246E2144}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Raw" sheetId="2" r:id="rId2"/>
+    <sheet name="LatLong" sheetId="3" r:id="rId2"/>
+    <sheet name="Raw" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$63</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="552">
   <si>
     <t>CITY</t>
   </si>
@@ -790,6 +791,912 @@
   </si>
   <si>
     <t>Dak Nong</t>
+  </si>
+  <si>
+    <t>Phân loại</t>
+  </si>
+  <si>
+    <t>Tên Tắt</t>
+  </si>
+  <si>
+    <t>DC name</t>
+  </si>
+  <si>
+    <t>Mã DC</t>
+  </si>
+  <si>
+    <t>DC_Number</t>
+  </si>
+  <si>
+    <t>Mã DC_CT</t>
+  </si>
+  <si>
+    <t>Địa chỉ</t>
+  </si>
+  <si>
+    <t>Tọa độ (kinh độ, vĩ độ)</t>
+  </si>
+  <si>
+    <t>Diện tích</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>Bình Thuận</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Bình Thuận</t>
+  </si>
+  <si>
+    <t>07. Bình Thuận</t>
+  </si>
+  <si>
+    <t>MTV</t>
+  </si>
+  <si>
+    <t>VHD</t>
+  </si>
+  <si>
+    <t>Thôn Vĩnh Sơn, xã Vĩnh Hảo, Tỉnh Lâm Đồng</t>
+  </si>
+  <si>
+    <t>11°16'37.5"N 108°44'04.2"E</t>
+  </si>
+  <si>
+    <t>Cần Thơ</t>
+  </si>
+  <si>
+    <t>Trung tâm Phân phối Cần Thơ</t>
+  </si>
+  <si>
+    <t>13. Hậu Giang Foods</t>
+  </si>
+  <si>
+    <t>MDQ</t>
+  </si>
+  <si>
+    <t>FHG</t>
+  </si>
+  <si>
+    <t>Kho Mekong, KCN Sông Hậu- Giai đoạn 1, xã Châu Thành, TP. Cần Thơ</t>
+  </si>
+  <si>
+    <t>9°57'53.1"N 105°50'57.9"E</t>
+  </si>
+  <si>
+    <t>Đà Nẵng</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Đà Nẵng</t>
+  </si>
+  <si>
+    <t>06. Đà Nẵng</t>
+  </si>
+  <si>
+    <t>MTN</t>
+  </si>
+  <si>
+    <t>DND</t>
+  </si>
+  <si>
+    <t>Kho Kim Thành Lợi, Đường Số 9, KCN Hòa Khánh, Phường Liên Chiểu, TP. Đà Nẵng</t>
+  </si>
+  <si>
+    <t>16°05'06.0"N 108°08'25.5"E</t>
+  </si>
+  <si>
+    <t>NM Net</t>
+  </si>
+  <si>
+    <t>Trung tâm Phân phối Đồng Nai</t>
+  </si>
+  <si>
+    <t>12. NETCO</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>Đường D4, KCN Lộc An - Bình Sơn, Xã Long Thành, Tỉnh Đồng Nai</t>
+  </si>
+  <si>
+    <t>10°47'12.5"N 106°59'29.8"E</t>
+  </si>
+  <si>
+    <t>Hải Dương</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Hải Dương</t>
+  </si>
+  <si>
+    <t>01. Hải Dương</t>
+  </si>
+  <si>
+    <t>MTS</t>
+  </si>
+  <si>
+    <t>HDD</t>
+  </si>
+  <si>
+    <t>Km 48+450, Quốc Lộ 5, Phường Việt Hòa, Thành Phố Hải Phòng</t>
+  </si>
+  <si>
+    <t>20°56'20.4"N 106°17'42.1"E</t>
+  </si>
+  <si>
+    <t>Hải Phòng</t>
+  </si>
+  <si>
+    <t>Trung tâm Phân phối Hải Phòng</t>
+  </si>
+  <si>
+    <t>05. Hải Phòng</t>
+  </si>
+  <si>
+    <t>MDV</t>
+  </si>
+  <si>
+    <t>HPD</t>
+  </si>
+  <si>
+    <t>Cổng 3 cảng nội địa hải dương, Km 48+450 Quốc lộ 5, Phường Việt Hòa, Thành phố Hải Phòng</t>
+  </si>
+  <si>
+    <t>20°49'10.0"N 106°46'39.4"E</t>
+  </si>
+  <si>
+    <t>Hậu Giang Beer</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Hậu Giang</t>
+  </si>
+  <si>
+    <t>14. Hậu Giang Beer</t>
+  </si>
+  <si>
+    <t>MBG</t>
+  </si>
+  <si>
+    <t>BHG</t>
+  </si>
+  <si>
+    <t>Khu Công Nghiệp Sông Hậu, Xã Châu Thành , Thành phố Cần Thơ</t>
+  </si>
+  <si>
+    <t>9°57'53.2"N 105°50'32.9"E</t>
+  </si>
+  <si>
+    <t>Hưng Yên</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Hưng Yên</t>
+  </si>
+  <si>
+    <t>02. Hưng Yên</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>V3W8+MFV, Xã Tân Lập, tỉnh Hưng Yên</t>
+  </si>
+  <si>
+    <t>20.89694354346599, 106.06626012649295</t>
+  </si>
+  <si>
+    <t>Thành Huy - Hưng Yên</t>
+  </si>
+  <si>
+    <t>Kho HY: nằm trong Cty Dịch Vụ Logictis Thành Huy - Q.Lộ 5A, Phường Đường Hào, Hưng Yên</t>
+  </si>
+  <si>
+    <t>20°55'45.0"N 106°04'02.2"E</t>
+  </si>
+  <si>
+    <t>Đông Dương - Hưng Yên</t>
+  </si>
+  <si>
+    <t>Thôn Tử Cầu, Xã Nguyễn Văn Linh, tỉnh Hưng Yên</t>
+  </si>
+  <si>
+    <t>20.954388190162952, 106.00570588741586</t>
+  </si>
+  <si>
+    <t>Nghệ An</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Nghệ An</t>
+  </si>
+  <si>
+    <t>03. Nghệ An</t>
+  </si>
+  <si>
+    <t>MTA</t>
+  </si>
+  <si>
+    <t>NAD</t>
+  </si>
+  <si>
+    <t>Khu A, Khu Nam Cấm, Khu Kinh Tế Đông Nam, Xã Trung Lộc, Nghệ An</t>
+  </si>
+  <si>
+    <t>18°49'42.5"N 105°39'24.7"E</t>
+  </si>
+  <si>
+    <t>Phú Yên</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Phú Yên</t>
+  </si>
+  <si>
+    <t>09. Phú Yên</t>
+  </si>
+  <si>
+    <t>MBN</t>
+  </si>
+  <si>
+    <t>BPY</t>
+  </si>
+  <si>
+    <t>Lô A12 - A14 Khu công nghiệp Hòa Hiệp, Phường Hòa Hiệp, Đắk Lắk</t>
+  </si>
+  <si>
+    <t>13°00'43.3"N 109°21'52.7"E</t>
+  </si>
+  <si>
+    <t>Quang Hanh</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Quang Hanh</t>
+  </si>
+  <si>
+    <t>04. Quang Hanh</t>
+  </si>
+  <si>
+    <t>QHD</t>
+  </si>
+  <si>
+    <t>Km 9, P. Quang Hanh, T. Quảng Ninh</t>
+  </si>
+  <si>
+    <t>21°00'11.9"N 107°13'25.8"E</t>
+  </si>
+  <si>
+    <t>TBS</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Sóng Thần - 3PLs</t>
+  </si>
+  <si>
+    <t>10. TBS</t>
+  </si>
+  <si>
+    <t>GMT</t>
+  </si>
+  <si>
+    <t>Đường DT743, Phường Dĩ An, TPHCM</t>
+  </si>
+  <si>
+    <t>10°55'33.6"N 106°44'40.5"E</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Sóng Thần - Inhouse</t>
+  </si>
+  <si>
+    <t>08. Kerry</t>
+  </si>
+  <si>
+    <t>MTD</t>
+  </si>
+  <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>Kho số 1, Tổng kho Kerry, đường số 18, KCN Sóng Thần 2, Phường Dĩ An, TPHCM</t>
+  </si>
+  <si>
+    <t>10°53'24.7"N 106°44'03.6"E</t>
+  </si>
+  <si>
+    <t>Suối Mơ</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Suối Mơ</t>
+  </si>
+  <si>
+    <t>SMD</t>
+  </si>
+  <si>
+    <t>Tổ 5, khu 8, P. Bãi Cháy, T. Quảng Ninh</t>
+  </si>
+  <si>
+    <t>20°57'38.9"N 107°01'40.1"E</t>
+  </si>
+  <si>
+    <t>Tanimex - Tân Bình</t>
+  </si>
+  <si>
+    <t>Trung Tâm Phân Phối Tân Bình</t>
+  </si>
+  <si>
+    <t>11. Tân Bình</t>
+  </si>
+  <si>
+    <t>MTF</t>
+  </si>
+  <si>
+    <t>HCM</t>
+  </si>
+  <si>
+    <t>Kho xưởng lô 1-6, Cụm 1, Đường M14, KCN Tân Bình, Phường Bình Hưng Hòa, TPHCM</t>
+  </si>
+  <si>
+    <t>10°49'14.4"N 106°36'50.7"E</t>
+  </si>
+  <si>
+    <t>Miền Núi - Tân Bình</t>
+  </si>
+  <si>
+    <t>Lô III 14, Đường số 1, Nhóm CN III, KCN Tân Bình, Phường Tây Thạnh, TPHCM</t>
+  </si>
+  <si>
+    <t>10.820919510037575, 106.61709947035497</t>
+  </si>
+  <si>
+    <t>Việt Tiến - Tân Bình</t>
+  </si>
+  <si>
+    <t>Lô III-10 Nhóm KCN III, KCN Tân Bình, Phường Tây Thạnh, TPHCM</t>
+  </si>
+  <si>
+    <t>Vân Trúc</t>
+  </si>
+  <si>
+    <t>Trung tâm phân phối Vân Trúc</t>
+  </si>
+  <si>
+    <t>08.1. Kho Vân Trúc</t>
+  </si>
+  <si>
+    <t>100/1G Khu Phố Đồng An 2, Phường Bình Hòa, TPHCM</t>
+  </si>
+  <si>
+    <t>10.898892302150536, 106.72275468517746</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>Trung tâm phân phối BW</t>
+  </si>
+  <si>
+    <t>08.2. Kho BW</t>
+  </si>
+  <si>
+    <t>15. Đồng Nai</t>
+  </si>
+  <si>
+    <t>DN2</t>
+  </si>
+  <si>
+    <t>VX24+662, Long Đức, Long Thành, Đồng Nai, Vietnam</t>
+  </si>
+  <si>
+    <t>10.851160102363028, 106.95547296357032</t>
+  </si>
+  <si>
+    <t>An Bình DCs</t>
+  </si>
+  <si>
+    <t>ABD</t>
+  </si>
+  <si>
+    <t>An Bình, Thành phố Biên Hòa, Đồng Nai</t>
+  </si>
+  <si>
+    <t>10.919767850139456, 106.85998435794458</t>
+  </si>
+  <si>
+    <t>Kho MML - Hà Nam</t>
+  </si>
+  <si>
+    <t>HYM</t>
+  </si>
+  <si>
+    <t>Đại Cương, Kim Bảng, Hà Nam</t>
+  </si>
+  <si>
+    <t>20.636496060714716, 105.88530447418114</t>
+  </si>
+  <si>
+    <t>Kho MML - Long An</t>
+  </si>
+  <si>
+    <t>LAM</t>
+  </si>
+  <si>
+    <t>Khu Công Nghiệp Tân Đức, Xã Hựu Thành, Huyện Đức Hòa, Tỉnh Long An</t>
+  </si>
+  <si>
+    <t>10.783012788829994, 106.46042287671807</t>
+  </si>
+  <si>
+    <t>Factory</t>
+  </si>
+  <si>
+    <t>Nhà máy Quang Hanh</t>
+  </si>
+  <si>
+    <t>QNW</t>
+  </si>
+  <si>
+    <t>Km9, Phường Quang Hanh, Thị Xã Cẩm Phả, Tỉnh Quảng Ninh</t>
+  </si>
+  <si>
+    <t>21.0082107, 107.2271147</t>
+  </si>
+  <si>
+    <t>21.0082107</t>
+  </si>
+  <si>
+    <t>107.2271147</t>
+  </si>
+  <si>
+    <t>Nhà máy Suối Mơ</t>
+  </si>
+  <si>
+    <t>SMW</t>
+  </si>
+  <si>
+    <t>Tổ 5, Khu 8, Phường Bãi Cháy, TP. Hạ Long, Tỉnh Quảng Ninh</t>
+  </si>
+  <si>
+    <t>20.9578941, 107.0832118</t>
+  </si>
+  <si>
+    <t>20.9578941</t>
+  </si>
+  <si>
+    <t>107.0832118</t>
+  </si>
+  <si>
+    <t>Nhà máy Hải Dương</t>
+  </si>
+  <si>
+    <t>MHD</t>
+  </si>
+  <si>
+    <t>Lô 22, KCN Đại An, TP. Hải Dương, Tỉnh Hải Dương</t>
+  </si>
+  <si>
+    <t>20.9297632, 106.2669247</t>
+  </si>
+  <si>
+    <t>20.9297632</t>
+  </si>
+  <si>
+    <t>106.2669247</t>
+  </si>
+  <si>
+    <t>Nhà máy gia công MSJ tại MHN</t>
+  </si>
+  <si>
+    <t>MCN</t>
+  </si>
+  <si>
+    <t>Lô CN-02, KCN Đồng Văn IV, Kim Bảng, Hà Nam</t>
+  </si>
+  <si>
+    <t>20.6378553, 105.8885067</t>
+  </si>
+  <si>
+    <t>20.6378553</t>
+  </si>
+  <si>
+    <t>105.8885067</t>
+  </si>
+  <si>
+    <t>Nhà máy sữa Elovi</t>
+  </si>
+  <si>
+    <t>ELO</t>
+  </si>
+  <si>
+    <t>KCN Nam Phổ Yên, Thuận Thành, Phổ Yên, Thái Nguyên</t>
+  </si>
+  <si>
+    <t>21.3340466, 105.8686921</t>
+  </si>
+  <si>
+    <t>21.3340466</t>
+  </si>
+  <si>
+    <t>105.8686921</t>
+  </si>
+  <si>
+    <t>Nhà máy Masan Miền Bắc</t>
+  </si>
+  <si>
+    <t>MMB</t>
+  </si>
+  <si>
+    <t>Khu B, Khu KT Đông Nam, Khu Công nghiệp Nam Cấm, xã Nghi Long, Huyện Nghi Lộc, tỉnh Nghệ An, Việt Nam</t>
+  </si>
+  <si>
+    <t>18.8333799, 105.6571789</t>
+  </si>
+  <si>
+    <t>18.8333799</t>
+  </si>
+  <si>
+    <t>105.6571789</t>
+  </si>
+  <si>
+    <t>Nhà máy Beer Phú Yên</t>
+  </si>
+  <si>
+    <t>PYB</t>
+  </si>
+  <si>
+    <t>Lô A12 - A14 - KCN Hòa Hiệp, Xã Hòa Hiệp Bắc, Huyện Đông Hòa, Tỉnh Phú Yên</t>
+  </si>
+  <si>
+    <t>13.013859, 109.3619624</t>
+  </si>
+  <si>
+    <t>13.013859</t>
+  </si>
+  <si>
+    <t>109.3619624</t>
+  </si>
+  <si>
+    <t>Nhà máy Vĩnh Hảo</t>
+  </si>
+  <si>
+    <t>VHC</t>
+  </si>
+  <si>
+    <t>Thôn Vĩnh Sơn, Xã Vĩnh Hảo, Huyện Tuy Phong, Tỉnh Bình Thuận</t>
+  </si>
+  <si>
+    <t>11.3132444, 108.7534139</t>
+  </si>
+  <si>
+    <t>11.3132444</t>
+  </si>
+  <si>
+    <t>108.7534139</t>
+  </si>
+  <si>
+    <t>Nhà máy Vĩnh Hảo B20L</t>
+  </si>
+  <si>
+    <t>V20</t>
+  </si>
+  <si>
+    <t>Nhà máy VCF Biên Hòa</t>
+  </si>
+  <si>
+    <t>VCF</t>
+  </si>
+  <si>
+    <t>KCN Biên Hòa 1, Phường An Bình, TP. Biên Hòa, Tỉnh Đồng Nai</t>
+  </si>
+  <si>
+    <t>10.921125, 106.8613515</t>
+  </si>
+  <si>
+    <t>10.921125</t>
+  </si>
+  <si>
+    <t>106.8613515</t>
+  </si>
+  <si>
+    <t>Nhà máy VCF Long Thành</t>
+  </si>
+  <si>
+    <t>VLT</t>
+  </si>
+  <si>
+    <t>KCN Long Thành, Xã Tam An, Huyện Long Thành, Tỉnh Đồng Nai</t>
+  </si>
+  <si>
+    <t>10.8312488, 106.935861</t>
+  </si>
+  <si>
+    <t>10.8312488</t>
+  </si>
+  <si>
+    <t>106.935861</t>
+  </si>
+  <si>
+    <t>Nhà máy NET Long Thành</t>
+  </si>
+  <si>
+    <t>Đường D4, KCN Lộc An - Bình Sơn, Xã Bình Sơn, Huyện Long Thành, Tỉnh Đồng Nai</t>
+  </si>
+  <si>
+    <t>10.7948211, 106.9900006</t>
+  </si>
+  <si>
+    <t>10.7948211</t>
+  </si>
+  <si>
+    <t>106.9900006</t>
+  </si>
+  <si>
+    <t>Nhà máy MSI</t>
+  </si>
+  <si>
+    <t>MSI</t>
+  </si>
+  <si>
+    <t>Lô IV, KCN Tân Đông Hiệp A, Phường Tân Đông Hiệp, Dĩ An, Bình Dương</t>
+  </si>
+  <si>
+    <t>10.92273, 106.7878992</t>
+  </si>
+  <si>
+    <t>10.92273</t>
+  </si>
+  <si>
+    <t>106.7878992</t>
+  </si>
+  <si>
+    <t>Nhà máy gia công MSJ tại SNF</t>
+  </si>
+  <si>
+    <t>MSJ</t>
+  </si>
+  <si>
+    <t>Nhà máy Vihawa Sóng Thần</t>
+  </si>
+  <si>
+    <t>SNF</t>
+  </si>
+  <si>
+    <t>Lô K4, Đường số 2, KCN Sóng Thần 2, Dĩ An, Bình Dương</t>
+  </si>
+  <si>
+    <t>10.8798866, 106.7507199</t>
+  </si>
+  <si>
+    <t>10.8798866</t>
+  </si>
+  <si>
+    <t>106.7507199</t>
+  </si>
+  <si>
+    <t>Nhà máy gia công VTF - Vihawa</t>
+  </si>
+  <si>
+    <t>VTF</t>
+  </si>
+  <si>
+    <t>Lô số III-10, Đường số 1, Nhóm CNIII, KCN Tân Bình, P. Tây Thạnh, Quận Tân Phú, TPHCM</t>
+  </si>
+  <si>
+    <t>10.8162555, 106.6251124</t>
+  </si>
+  <si>
+    <t>10.8162555</t>
+  </si>
+  <si>
+    <t>106.6251124</t>
+  </si>
+  <si>
+    <t>Nhà máy gia công Cao Nguyên Xanh</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>Tổ 2, Ấp Phú Lợi, Tân Phú Trung, Củ Chi, TP.HCM</t>
+  </si>
+  <si>
+    <t>10.953763, 106.5476008</t>
+  </si>
+  <si>
+    <t>10.953763</t>
+  </si>
+  <si>
+    <t>106.5476008</t>
+  </si>
+  <si>
+    <t>Nhà máy Gia công Nihon</t>
+  </si>
+  <si>
+    <t>NCP</t>
+  </si>
+  <si>
+    <t>Lô F-5-CN, KCN Mỹ Phước 2, Thị Xã Bến Cát, Bình Dương</t>
+  </si>
+  <si>
+    <t>11.1320152, 106.6306686</t>
+  </si>
+  <si>
+    <t>11.1320152</t>
+  </si>
+  <si>
+    <t>106.6306686</t>
+  </si>
+  <si>
+    <t>Nhà máy Hậu Giang Food</t>
+  </si>
+  <si>
+    <t>MHG</t>
+  </si>
+  <si>
+    <t>KCN Sông Hậu, Xã Đông Phú, Huyện Châu Thành, Hậu Giang</t>
+  </si>
+  <si>
+    <t>9.9610889, 105.8424</t>
+  </si>
+  <si>
+    <t>9.9610889</t>
+  </si>
+  <si>
+    <t>105.8424</t>
+  </si>
+  <si>
+    <t>Nhà máy Hậu Giang Beer</t>
+  </si>
+  <si>
+    <t>HGB</t>
+  </si>
+  <si>
+    <t>Nhà máy Nam Ngư Phú Quốc, Masan Phú Quốc</t>
+  </si>
+  <si>
+    <t>NPQ</t>
+  </si>
+  <si>
+    <t>Tổ 1 Ấp Suối Đá, Xã Dương Tơ, Huyện Phú Quốc, Tỉnh Kiên Giang</t>
+  </si>
+  <si>
+    <t>10.1253417, 103.9956269</t>
+  </si>
+  <si>
+    <t>10.1253417</t>
+  </si>
+  <si>
+    <t>103.9956269</t>
+  </si>
+  <si>
+    <t>Nhà máy Hương Giang Lagi</t>
+  </si>
+  <si>
+    <t>HGC</t>
+  </si>
+  <si>
+    <t>Thôn Bình An 2, Xã Tân Bình, Thị xã La Gi, Tỉnh Bình Thuận, Việt Nam</t>
+  </si>
+  <si>
+    <t>10.6940278, 107.7769455</t>
+  </si>
+  <si>
+    <t>10.6940278</t>
+  </si>
+  <si>
+    <t>107.7769455</t>
+  </si>
+  <si>
+    <t>Nhà máy gia công Deneast</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>Số 7 VSIP II-A, Đường 31, Xã Vĩnh Tân, Thị Xã Tân Uyên, Bình Dương</t>
+  </si>
+  <si>
+    <t>11.1379247, 106.6978593</t>
+  </si>
+  <si>
+    <t>11.1379247</t>
+  </si>
+  <si>
+    <t>106.6978593</t>
+  </si>
+  <si>
+    <t>Nhà máy gia công OCM tại Việt Nam</t>
+  </si>
+  <si>
+    <t>OCM</t>
+  </si>
+  <si>
+    <t>Đức Lập Hạ, Đức Hòa, Long An</t>
+  </si>
+  <si>
+    <t>10.9153529, 106.4409484</t>
+  </si>
+  <si>
+    <t>10.9153529</t>
+  </si>
+  <si>
+    <t>106.4409484</t>
+  </si>
+  <si>
+    <t>Sản phẩm nhập khẩu về tại DC</t>
+  </si>
+  <si>
+    <t>IMP</t>
+  </si>
+  <si>
+    <t>Sản phẩm nhập khẩu từ NCC</t>
+  </si>
+  <si>
+    <t>Nhà máy gia công Aroma</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
+    <t>Đông Sơn, Huyện Thủy Nguyên, TP Hải Phòng</t>
+  </si>
+  <si>
+    <t>20.9376842, 106.6556575</t>
+  </si>
+  <si>
+    <t>20.9376842</t>
+  </si>
+  <si>
+    <t>106.6556575</t>
+  </si>
+  <si>
+    <t>Nhà máy gia công Godaco Bến Tre</t>
+  </si>
+  <si>
+    <t>BTG</t>
+  </si>
+  <si>
+    <t>Lô A19-20, KCN An Hiệp, xã Tường Đa, huyện Châu Thành, tỉnh Bến Tre</t>
+  </si>
+  <si>
+    <t>10.2797839, 106.3007738</t>
+  </si>
+  <si>
+    <t>10.2797839</t>
+  </si>
+  <si>
+    <t>106.3007738</t>
+  </si>
+  <si>
+    <t>Nhà máy gia công tại Long An</t>
+  </si>
+  <si>
+    <t>LAG</t>
+  </si>
+  <si>
+    <t>10.8104615, 106.4751146</t>
+  </si>
+  <si>
+    <t>10.8104615</t>
+  </si>
+  <si>
+    <t>106.4751146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đồng Nai </t>
+  </si>
+  <si>
+    <t>Tên</t>
   </si>
 </sst>
 </file>
@@ -800,7 +1707,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -834,6 +1741,19 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="18">
@@ -940,7 +1860,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -974,12 +1894,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1029,6 +1962,14 @@
     <xf numFmtId="164" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2350,6 +3291,1748 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19E4313E-4D21-40CA-89A2-E937E401BC57}">
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="78.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>551</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="F2" s="24">
+        <v>8155001</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="J2" s="24">
+        <v>6050</v>
+      </c>
+      <c r="K2" s="24">
+        <v>11.277082999999999</v>
+      </c>
+      <c r="L2" s="24">
+        <v>108.7345</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="F3" s="24">
+        <v>8169001</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="J3" s="24">
+        <v>4770</v>
+      </c>
+      <c r="K3" s="24">
+        <v>9.9647500000000004</v>
+      </c>
+      <c r="L3" s="24">
+        <v>105.849417</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="F4" s="24">
+        <v>8156001</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="J4" s="24">
+        <v>3600</v>
+      </c>
+      <c r="K4" s="24">
+        <v>16.085000000000001</v>
+      </c>
+      <c r="L4" s="24">
+        <v>108.140417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="F5" s="24">
+        <v>8167001</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="J5" s="24">
+        <v>12943</v>
+      </c>
+      <c r="K5" s="24">
+        <v>10.786806</v>
+      </c>
+      <c r="L5" s="24">
+        <v>106.99161100000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="F6" s="24">
+        <v>8157001</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J6" s="24">
+        <v>8196</v>
+      </c>
+      <c r="K6" s="24">
+        <v>20.939</v>
+      </c>
+      <c r="L6" s="24">
+        <v>106.295028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="F7" s="24">
+        <v>8170001</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="J7" s="24">
+        <v>5880</v>
+      </c>
+      <c r="K7" s="24">
+        <v>20.819444000000001</v>
+      </c>
+      <c r="L7" s="24">
+        <v>106.77761099999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="F8" s="24">
+        <v>8158001</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="J8" s="24">
+        <v>1000</v>
+      </c>
+      <c r="K8" s="24">
+        <v>9.9647780000000008</v>
+      </c>
+      <c r="L8" s="24">
+        <v>105.842472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="F9" s="24">
+        <v>8159001</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="J9" s="24">
+        <v>6023.36</v>
+      </c>
+      <c r="K9" s="24">
+        <v>20.896944000000001</v>
+      </c>
+      <c r="L9" s="24">
+        <v>106.06626</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="F10" s="24">
+        <v>8159001</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>320</v>
+      </c>
+      <c r="J10" s="24">
+        <v>15196</v>
+      </c>
+      <c r="K10" s="24">
+        <v>20.929167</v>
+      </c>
+      <c r="L10" s="24">
+        <v>106.067278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="F11" s="24">
+        <v>8159001</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="J11" s="24">
+        <v>5000</v>
+      </c>
+      <c r="K11" s="24">
+        <v>20.954388000000002</v>
+      </c>
+      <c r="L11" s="24">
+        <v>106.005706</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="F12" s="24">
+        <v>8160001</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="J12" s="24">
+        <v>15400</v>
+      </c>
+      <c r="K12" s="24">
+        <v>18.828472000000001</v>
+      </c>
+      <c r="L12" s="24">
+        <v>105.65686100000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>334</v>
+      </c>
+      <c r="F13" s="24">
+        <v>8161001</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="J13" s="24">
+        <v>1000</v>
+      </c>
+      <c r="K13" s="24">
+        <v>13.011972</v>
+      </c>
+      <c r="L13" s="24">
+        <v>109.364639</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>338</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="F14" s="24">
+        <v>8162001</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="J14" s="24">
+        <v>900</v>
+      </c>
+      <c r="K14" s="24">
+        <v>21.003305999999998</v>
+      </c>
+      <c r="L14" s="24">
+        <v>107.223833</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="F15" s="24">
+        <v>8164001</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="J15" s="24">
+        <v>20000</v>
+      </c>
+      <c r="K15" s="24">
+        <v>10.926</v>
+      </c>
+      <c r="L15" s="24">
+        <v>106.74458300000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="F16" s="24">
+        <v>8163001</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="J16" s="24">
+        <v>28984</v>
+      </c>
+      <c r="K16" s="24">
+        <v>10.890193999999999</v>
+      </c>
+      <c r="L16" s="24">
+        <v>106.73433300000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24" t="s">
+        <v>359</v>
+      </c>
+      <c r="F17" s="24">
+        <v>8165001</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>359</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>360</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="J17" s="24">
+        <v>730</v>
+      </c>
+      <c r="K17" s="24">
+        <v>20.960806000000002</v>
+      </c>
+      <c r="L17" s="24">
+        <v>107.027806</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B18" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="F18" s="24">
+        <v>8166001</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="J18" s="24">
+        <v>7700</v>
+      </c>
+      <c r="K18" s="24">
+        <v>10.820667</v>
+      </c>
+      <c r="L18" s="24">
+        <v>106.61408299999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="F19" s="24">
+        <v>8166001</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="J19" s="24">
+        <v>250</v>
+      </c>
+      <c r="K19" s="24">
+        <v>10.820919999999999</v>
+      </c>
+      <c r="L19" s="24">
+        <v>106.617099</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="F20" s="24">
+        <v>8166001</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="J20" s="24">
+        <v>570</v>
+      </c>
+      <c r="K20" s="24">
+        <v>10.820919999999999</v>
+      </c>
+      <c r="L20" s="24">
+        <v>106.617099</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>374</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>375</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="F21" s="24">
+        <v>8171001</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>377</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>378</v>
+      </c>
+      <c r="J21" s="24">
+        <v>3850</v>
+      </c>
+      <c r="K21" s="24">
+        <v>10.898892</v>
+      </c>
+      <c r="L21" s="24">
+        <v>106.72275500000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>380</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>381</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24">
+        <v>3850</v>
+      </c>
+      <c r="K22" s="24">
+        <v>10.898892</v>
+      </c>
+      <c r="L22" s="24">
+        <v>106.72275500000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>384</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24">
+        <v>10.851160102363</v>
+      </c>
+      <c r="L23" s="24">
+        <v>106.95547296357</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24" t="s">
+        <v>386</v>
+      </c>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24" t="s">
+        <v>387</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>388</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24">
+        <v>10.919767850139401</v>
+      </c>
+      <c r="L24" s="24">
+        <v>106.859984357944</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="I25" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24">
+        <v>20.636496060714698</v>
+      </c>
+      <c r="L25" s="24">
+        <v>105.885304474181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24" t="s">
+        <v>395</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>396</v>
+      </c>
+      <c r="I26" s="24" t="s">
+        <v>397</v>
+      </c>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24">
+        <v>10.7830127888299</v>
+      </c>
+      <c r="L26" s="24">
+        <v>106.460422876718</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24" t="s">
+        <v>400</v>
+      </c>
+      <c r="H27" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>402</v>
+      </c>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24" t="s">
+        <v>403</v>
+      </c>
+      <c r="L27" s="24" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24" t="s">
+        <v>405</v>
+      </c>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="H28" s="24" t="s">
+        <v>407</v>
+      </c>
+      <c r="I28" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="L28" s="24" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24" t="s">
+        <v>412</v>
+      </c>
+      <c r="H29" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="I29" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="L29" s="24" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="I30" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="L30" s="24" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="H31" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="I31" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24" t="s">
+        <v>427</v>
+      </c>
+      <c r="L31" s="24" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A32" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24" t="s">
+        <v>430</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="I32" s="24" t="s">
+        <v>432</v>
+      </c>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="L32" s="24" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A33" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24" t="s">
+        <v>435</v>
+      </c>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>437</v>
+      </c>
+      <c r="I33" s="24" t="s">
+        <v>438</v>
+      </c>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="L33" s="24" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A34" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24" t="s">
+        <v>441</v>
+      </c>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24" t="s">
+        <v>442</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>444</v>
+      </c>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24" t="s">
+        <v>445</v>
+      </c>
+      <c r="L34" s="24" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A35" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="I35" s="24" t="s">
+        <v>444</v>
+      </c>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24" t="s">
+        <v>445</v>
+      </c>
+      <c r="L35" s="24" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A36" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24" t="s">
+        <v>449</v>
+      </c>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>451</v>
+      </c>
+      <c r="I36" s="24" t="s">
+        <v>452</v>
+      </c>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24" t="s">
+        <v>453</v>
+      </c>
+      <c r="L36" s="24" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A37" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="H37" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="I37" s="24" t="s">
+        <v>458</v>
+      </c>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24" t="s">
+        <v>459</v>
+      </c>
+      <c r="L37" s="24" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>462</v>
+      </c>
+      <c r="I38" s="24" t="s">
+        <v>463</v>
+      </c>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="L38" s="24" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A39" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24" t="s">
+        <v>467</v>
+      </c>
+      <c r="H39" s="24" t="s">
+        <v>468</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24" t="s">
+        <v>470</v>
+      </c>
+      <c r="L39" s="24" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A40" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24" t="s">
+        <v>472</v>
+      </c>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="H40" s="24" t="s">
+        <v>468</v>
+      </c>
+      <c r="I40" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24" t="s">
+        <v>470</v>
+      </c>
+      <c r="L40" s="24" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A41" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24" t="s">
+        <v>474</v>
+      </c>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24" t="s">
+        <v>475</v>
+      </c>
+      <c r="H41" s="24" t="s">
+        <v>476</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>477</v>
+      </c>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24" t="s">
+        <v>478</v>
+      </c>
+      <c r="L41" s="24" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A42" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24" t="s">
+        <v>480</v>
+      </c>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="H42" s="24" t="s">
+        <v>482</v>
+      </c>
+      <c r="I42" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="L42" s="24" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A43" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="H43" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="I43" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="J43" s="24"/>
+      <c r="K43" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="L43" s="24" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A44" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24" t="s">
+        <v>492</v>
+      </c>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="I44" s="24" t="s">
+        <v>495</v>
+      </c>
+      <c r="J44" s="24"/>
+      <c r="K44" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="L44" s="24" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A45" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24" t="s">
+        <v>498</v>
+      </c>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24" t="s">
+        <v>499</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>500</v>
+      </c>
+      <c r="I45" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="J45" s="24"/>
+      <c r="K45" s="24" t="s">
+        <v>502</v>
+      </c>
+      <c r="L45" s="24" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A46" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24" t="s">
+        <v>504</v>
+      </c>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="H46" s="24" t="s">
+        <v>500</v>
+      </c>
+      <c r="I46" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="J46" s="24"/>
+      <c r="K46" s="24" t="s">
+        <v>502</v>
+      </c>
+      <c r="L46" s="24" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A47" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24" t="s">
+        <v>506</v>
+      </c>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24" t="s">
+        <v>507</v>
+      </c>
+      <c r="H47" s="24" t="s">
+        <v>508</v>
+      </c>
+      <c r="I47" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="J47" s="24"/>
+      <c r="K47" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="L47" s="24" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A48" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24" t="s">
+        <v>512</v>
+      </c>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24" t="s">
+        <v>513</v>
+      </c>
+      <c r="H48" s="24" t="s">
+        <v>514</v>
+      </c>
+      <c r="I48" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="J48" s="24"/>
+      <c r="K48" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="L48" s="24" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A49" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="H49" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="I49" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="J49" s="24"/>
+      <c r="K49" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="L49" s="24" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A50" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24" t="s">
+        <v>525</v>
+      </c>
+      <c r="H50" s="24" t="s">
+        <v>526</v>
+      </c>
+      <c r="I50" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="J50" s="24"/>
+      <c r="K50" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="L50" s="24" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A51" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B51" s="24"/>
+      <c r="C51" s="24" t="s">
+        <v>530</v>
+      </c>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="I51" s="24"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="24"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A52" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24" t="s">
+        <v>533</v>
+      </c>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24" t="s">
+        <v>534</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>535</v>
+      </c>
+      <c r="I52" s="24" t="s">
+        <v>536</v>
+      </c>
+      <c r="J52" s="24"/>
+      <c r="K52" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="L52" s="24" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A53" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24" t="s">
+        <v>540</v>
+      </c>
+      <c r="H53" s="24" t="s">
+        <v>541</v>
+      </c>
+      <c r="I53" s="24" t="s">
+        <v>542</v>
+      </c>
+      <c r="J53" s="24"/>
+      <c r="K53" s="24" t="s">
+        <v>543</v>
+      </c>
+      <c r="L53" s="24" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A54" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24" t="s">
+        <v>545</v>
+      </c>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="H54" s="24" t="s">
+        <v>396</v>
+      </c>
+      <c r="I54" s="24" t="s">
+        <v>547</v>
+      </c>
+      <c r="J54" s="24"/>
+      <c r="K54" s="24" t="s">
+        <v>548</v>
+      </c>
+      <c r="L54" s="24" t="s">
+        <v>549</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA715D7-FFFA-4576-8F67-7F5C67294773}">
   <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/map/DC_Province.xlsx
+++ b/map/DC_Province.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2c7edca7daaa657/Image/Hình ảnh/ThanhPhat_Masan/DC FMCG/org/map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{69D89A4B-C117-4522-9C42-D6F8D84E04A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6D9D1FD-F9CC-440E-B1A3-6E7E246E2144}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{69D89A4B-C117-4522-9C42-D6F8D84E04A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB649D6-131A-46C0-9B97-1C982FDA7A7E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="560">
   <si>
     <t>CITY</t>
   </si>
@@ -1111,9 +1111,6 @@
     <t>Kho số 1, Tổng kho Kerry, đường số 18, KCN Sóng Thần 2, Phường Dĩ An, TPHCM</t>
   </si>
   <si>
-    <t>10°53'24.7"N 106°44'03.6"E</t>
-  </si>
-  <si>
     <t>Suối Mơ</t>
   </si>
   <si>
@@ -1147,18 +1144,12 @@
     <t>Kho xưởng lô 1-6, Cụm 1, Đường M14, KCN Tân Bình, Phường Bình Hưng Hòa, TPHCM</t>
   </si>
   <si>
-    <t>10°49'14.4"N 106°36'50.7"E</t>
-  </si>
-  <si>
     <t>Miền Núi - Tân Bình</t>
   </si>
   <si>
     <t>Lô III 14, Đường số 1, Nhóm CN III, KCN Tân Bình, Phường Tây Thạnh, TPHCM</t>
   </si>
   <si>
-    <t>10.820919510037575, 106.61709947035497</t>
-  </si>
-  <si>
     <t>Việt Tiến - Tân Bình</t>
   </si>
   <si>
@@ -1177,9 +1168,6 @@
     <t>100/1G Khu Phố Đồng An 2, Phường Bình Hòa, TPHCM</t>
   </si>
   <si>
-    <t>10.898892302150536, 106.72275468517746</t>
-  </si>
-  <si>
     <t>BW</t>
   </si>
   <si>
@@ -1450,15 +1438,6 @@
     <t>Lô IV, KCN Tân Đông Hiệp A, Phường Tân Đông Hiệp, Dĩ An, Bình Dương</t>
   </si>
   <si>
-    <t>10.92273, 106.7878992</t>
-  </si>
-  <si>
-    <t>10.92273</t>
-  </si>
-  <si>
-    <t>106.7878992</t>
-  </si>
-  <si>
     <t>Nhà máy gia công MSJ tại SNF</t>
   </si>
   <si>
@@ -1693,10 +1672,55 @@
     <t>106.4751146</t>
   </si>
   <si>
-    <t xml:space="preserve">Đồng Nai </t>
-  </si>
-  <si>
     <t>Tên</t>
+  </si>
+  <si>
+    <t>10.89879535831198, 106.75413297737968</t>
+  </si>
+  <si>
+    <t>10.89879535831198</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 106.75413297737968</t>
+  </si>
+  <si>
+    <t>10.820549167651448, 106.61395872263057</t>
+  </si>
+  <si>
+    <t>10.820549167651448</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 106.61395872263057</t>
+  </si>
+  <si>
+    <t>10.889696291065894, 106.73420976703588</t>
+  </si>
+  <si>
+    <t>10.889696291065894</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 106.73420976703588</t>
+  </si>
+  <si>
+    <t>10.924485478734782, 106.77731002642267</t>
+  </si>
+  <si>
+    <t>10.924485478734782</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 106.77731002642267</t>
+  </si>
+  <si>
+    <t>Đồng Nai</t>
+  </si>
+  <si>
+    <t>10.905287321133404, 106.78710144342529</t>
+  </si>
+  <si>
+    <t>10.905287321133404</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 106.78710144342529</t>
   </si>
 </sst>
 </file>
@@ -3315,7 +3339,7 @@
         <v>251</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="D1" s="22" t="s">
         <v>252</v>
@@ -3903,16 +3927,16 @@
         <v>355</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>356</v>
+        <v>544</v>
       </c>
       <c r="J16" s="24">
         <v>28984</v>
       </c>
-      <c r="K16" s="24">
-        <v>10.890193999999999</v>
-      </c>
-      <c r="L16" s="24">
-        <v>106.73433300000001</v>
+      <c r="K16" s="24" t="s">
+        <v>545</v>
+      </c>
+      <c r="L16" s="24" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
@@ -3920,26 +3944,26 @@
         <v>261</v>
       </c>
       <c r="B17" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>357</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>358</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F17" s="24">
         <v>8165001</v>
       </c>
       <c r="G17" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="H17" s="24" t="s">
         <v>359</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="I17" s="24" t="s">
         <v>360</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>361</v>
       </c>
       <c r="J17" s="24">
         <v>730</v>
@@ -3956,37 +3980,37 @@
         <v>261</v>
       </c>
       <c r="B18" t="s">
+        <v>361</v>
+      </c>
+      <c r="C18" s="24" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="D18" s="24" t="s">
         <v>363</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="E18" s="24" t="s">
         <v>364</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>365</v>
       </c>
       <c r="F18" s="24">
         <v>8166001</v>
       </c>
       <c r="G18" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="H18" s="24" t="s">
         <v>366</v>
       </c>
-      <c r="H18" s="24" t="s">
-        <v>367</v>
-      </c>
       <c r="I18" s="24" t="s">
-        <v>368</v>
+        <v>547</v>
       </c>
       <c r="J18" s="24">
         <v>7700</v>
       </c>
-      <c r="K18" s="24">
-        <v>10.820667</v>
-      </c>
-      <c r="L18" s="24">
-        <v>106.61408299999999</v>
+      <c r="K18" s="24" t="s">
+        <v>548</v>
+      </c>
+      <c r="L18" s="24" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -3994,37 +4018,37 @@
         <v>261</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C19" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>363</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="E19" s="24" t="s">
         <v>364</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>365</v>
       </c>
       <c r="F19" s="24">
         <v>8166001</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>371</v>
+        <v>547</v>
       </c>
       <c r="J19" s="24">
         <v>250</v>
       </c>
-      <c r="K19" s="24">
-        <v>10.820919999999999</v>
-      </c>
-      <c r="L19" s="24">
-        <v>106.617099</v>
+      <c r="K19" s="24" t="s">
+        <v>548</v>
+      </c>
+      <c r="L19" s="24" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
@@ -4032,37 +4056,37 @@
         <v>261</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C20" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="D20" s="24" t="s">
         <v>363</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="E20" s="24" t="s">
         <v>364</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>365</v>
       </c>
       <c r="F20" s="24">
         <v>8166001</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>371</v>
+        <v>547</v>
       </c>
       <c r="J20" s="24">
         <v>570</v>
       </c>
-      <c r="K20" s="24">
-        <v>10.820919999999999</v>
-      </c>
-      <c r="L20" s="24">
-        <v>106.617099</v>
+      <c r="K20" s="24" t="s">
+        <v>548</v>
+      </c>
+      <c r="L20" s="24" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
@@ -4070,13 +4094,13 @@
         <v>261</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>353</v>
@@ -4088,19 +4112,19 @@
         <v>354</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>378</v>
+        <v>550</v>
       </c>
       <c r="J21" s="24">
         <v>3850</v>
       </c>
-      <c r="K21" s="24">
-        <v>10.898892</v>
-      </c>
-      <c r="L21" s="24">
-        <v>106.72275500000001</v>
+      <c r="K21" s="24" t="s">
+        <v>551</v>
+      </c>
+      <c r="L21" s="24" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -4108,13 +4132,13 @@
         <v>261</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>353</v>
@@ -4124,15 +4148,17 @@
         <v>354</v>
       </c>
       <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
+      <c r="I22" s="24" t="s">
+        <v>553</v>
+      </c>
       <c r="J22" s="24">
         <v>3850</v>
       </c>
-      <c r="K22" s="24">
-        <v>10.898892</v>
-      </c>
-      <c r="L22" s="24">
-        <v>106.72275500000001</v>
+      <c r="K22" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
@@ -4140,22 +4166,22 @@
         <v>261</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C23" s="24"/>
       <c r="D23" s="24" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="24" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J23" s="24"/>
       <c r="K23" s="24">
@@ -4171,19 +4197,19 @@
       </c>
       <c r="B24" s="24"/>
       <c r="C24" s="24" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="24" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J24" s="24"/>
       <c r="K24" s="24">
@@ -4199,19 +4225,19 @@
       </c>
       <c r="B25" s="24"/>
       <c r="C25" s="24" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="24" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="J25" s="24"/>
       <c r="K25" s="24">
@@ -4227,19 +4253,19 @@
       </c>
       <c r="B26" s="24"/>
       <c r="C26" s="24" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="24" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="J26" s="24"/>
       <c r="K26" s="24">
@@ -4251,319 +4277,319 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B27" s="24"/>
       <c r="C27" s="24" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
       <c r="G27" s="24" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J27" s="24"/>
       <c r="K27" s="24" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="L27" s="24" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B28" s="24"/>
       <c r="C28" s="24" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24"/>
       <c r="F28" s="24"/>
       <c r="G28" s="24" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="J28" s="24"/>
       <c r="K28" s="24" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L28" s="24" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B29" s="24"/>
       <c r="C29" s="24" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24"/>
       <c r="F29" s="24"/>
       <c r="G29" s="24" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="J29" s="24"/>
       <c r="K29" s="24" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="L29" s="24" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B30" s="24"/>
       <c r="C30" s="24" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
       <c r="G30" s="24" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="I30" s="24" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="J30" s="24"/>
       <c r="K30" s="24" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="L30" s="24" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B31" s="24"/>
       <c r="C31" s="24" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="24" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="J31" s="24"/>
       <c r="K31" s="24" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="24" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" s="24" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="J32" s="24"/>
       <c r="K32" s="24" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L32" s="24" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B33" s="24"/>
       <c r="C33" s="24" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" s="24" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J33" s="24"/>
       <c r="K33" s="24" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="L33" s="24" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B34" s="24"/>
       <c r="C34" s="24" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
       <c r="F34" s="24"/>
       <c r="G34" s="24" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="J34" s="24"/>
       <c r="K34" s="24" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="L34" s="24" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B35" s="24"/>
       <c r="C35" s="24" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
       <c r="G35" s="24" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="I35" s="24" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="J35" s="24"/>
       <c r="K35" s="24" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="L35" s="24" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="24"/>
       <c r="F36" s="24"/>
       <c r="G36" s="24" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="I36" s="24" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="J36" s="24"/>
       <c r="K36" s="24" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="L36" s="24" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B37" s="24"/>
       <c r="C37" s="24" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D37" s="24"/>
       <c r="E37" s="24"/>
       <c r="F37" s="24"/>
       <c r="G37" s="24" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="I37" s="24" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="J37" s="24"/>
       <c r="K37" s="24" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="L37" s="24" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B38" s="24"/>
       <c r="C38" s="24" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D38" s="24"/>
       <c r="E38" s="24"/>
@@ -4572,371 +4598,371 @@
         <v>287</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="J38" s="24"/>
       <c r="K38" s="24" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="L38" s="24" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B39" s="24"/>
       <c r="C39" s="24" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24"/>
       <c r="F39" s="24"/>
       <c r="G39" s="24" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="I39" s="24" t="s">
-        <v>469</v>
+        <v>557</v>
       </c>
       <c r="J39" s="24"/>
       <c r="K39" s="24" t="s">
-        <v>470</v>
+        <v>558</v>
       </c>
       <c r="L39" s="24" t="s">
-        <v>471</v>
+        <v>559</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B40" s="24"/>
       <c r="C40" s="24" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
       <c r="F40" s="24"/>
       <c r="G40" s="24" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>469</v>
+        <v>557</v>
       </c>
       <c r="J40" s="24"/>
       <c r="K40" s="24" t="s">
-        <v>470</v>
+        <v>558</v>
       </c>
       <c r="L40" s="24" t="s">
-        <v>471</v>
+        <v>559</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B41" s="24"/>
       <c r="C41" s="24" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
       <c r="G41" s="24" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="J41" s="24"/>
       <c r="K41" s="24" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="L41" s="24" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B42" s="24"/>
       <c r="C42" s="24" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D42" s="24"/>
       <c r="E42" s="24"/>
       <c r="F42" s="24"/>
       <c r="G42" s="24" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="J42" s="24"/>
       <c r="K42" s="24" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B43" s="24"/>
       <c r="C43" s="24" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="D43" s="24"/>
       <c r="E43" s="24"/>
       <c r="F43" s="24"/>
       <c r="G43" s="24" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="J43" s="24"/>
       <c r="K43" s="24" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="L43" s="24" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B44" s="24"/>
       <c r="C44" s="24" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="24"/>
       <c r="F44" s="24"/>
       <c r="G44" s="24" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="I44" s="24" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J44" s="24"/>
       <c r="K44" s="24" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="L44" s="24" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B45" s="24"/>
       <c r="C45" s="24" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="D45" s="24"/>
       <c r="E45" s="24"/>
       <c r="F45" s="24"/>
       <c r="G45" s="24" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="I45" s="24" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="J45" s="24"/>
       <c r="K45" s="24" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="L45" s="24" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B46" s="24"/>
       <c r="C46" s="24" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="D46" s="24"/>
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
       <c r="G46" s="24" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="J46" s="24"/>
       <c r="K46" s="24" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="L46" s="24" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B47" s="24"/>
       <c r="C47" s="24" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="D47" s="24"/>
       <c r="E47" s="24"/>
       <c r="F47" s="24"/>
       <c r="G47" s="24" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="J47" s="24"/>
       <c r="K47" s="24" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="L47" s="24" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="24" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="24"/>
       <c r="F48" s="24"/>
       <c r="G48" s="24" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="J48" s="24"/>
       <c r="K48" s="24" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="L48" s="24" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B49" s="24"/>
       <c r="C49" s="24" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="D49" s="24"/>
       <c r="E49" s="24"/>
       <c r="F49" s="24"/>
       <c r="G49" s="24" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="J49" s="24"/>
       <c r="K49" s="24" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="L49" s="24" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B50" s="24"/>
       <c r="C50" s="24" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="D50" s="24"/>
       <c r="E50" s="24"/>
       <c r="F50" s="24"/>
       <c r="G50" s="24" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="J50" s="24"/>
       <c r="K50" s="24" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="L50" s="24" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B51" s="24"/>
       <c r="C51" s="24" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="D51" s="24"/>
       <c r="E51" s="24"/>
       <c r="F51" s="24"/>
       <c r="G51" s="24" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="I51" s="24"/>
       <c r="J51" s="24"/>
@@ -4945,86 +4971,86 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B52" s="24"/>
       <c r="C52" s="24" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="D52" s="24"/>
       <c r="E52" s="24"/>
       <c r="F52" s="24"/>
       <c r="G52" s="24" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="J52" s="24"/>
       <c r="K52" s="24" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="L52" s="24" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B53" s="24"/>
       <c r="C53" s="24" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="D53" s="24"/>
       <c r="E53" s="24"/>
       <c r="F53" s="24"/>
       <c r="G53" s="24" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="J53" s="24"/>
       <c r="K53" s="24" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="L53" s="24" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B54" s="24"/>
       <c r="C54" s="24" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="D54" s="24"/>
       <c r="E54" s="24"/>
       <c r="F54" s="24"/>
       <c r="G54" s="24" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="J54" s="24"/>
       <c r="K54" s="24" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="L54" s="24" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>

--- a/map/DC_Province.xlsx
+++ b/map/DC_Province.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2c7edca7daaa657/Image/Hình ảnh/ThanhPhat_Masan/DC FMCG/org/map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{69D89A4B-C117-4522-9C42-D6F8D84E04A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB649D6-131A-46C0-9B97-1C982FDA7A7E}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{69D89A4B-C117-4522-9C42-D6F8D84E04A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{714E2F87-95B6-4DF1-83F3-AEAD2C80DE9A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="552">
   <si>
     <t>CITY</t>
   </si>
@@ -850,9 +850,6 @@
     <t>11°16'37.5"N 108°44'04.2"E</t>
   </si>
   <si>
-    <t>Cần Thơ</t>
-  </si>
-  <si>
     <t>Trung tâm Phân phối Cần Thơ</t>
   </si>
   <si>
@@ -892,9 +889,6 @@
     <t>16°05'06.0"N 108°08'25.5"E</t>
   </si>
   <si>
-    <t>NM Net</t>
-  </si>
-  <si>
     <t>Trung tâm Phân phối Đồng Nai</t>
   </si>
   <si>
@@ -1186,9 +1180,6 @@
     <t>VX24+662, Long Đức, Long Thành, Đồng Nai, Vietnam</t>
   </si>
   <si>
-    <t>10.851160102363028, 106.95547296357032</t>
-  </si>
-  <si>
     <t>An Bình DCs</t>
   </si>
   <si>
@@ -1198,9 +1189,6 @@
     <t>An Bình, Thành phố Biên Hòa, Đồng Nai</t>
   </si>
   <si>
-    <t>10.919767850139456, 106.85998435794458</t>
-  </si>
-  <si>
     <t>Kho MML - Hà Nam</t>
   </si>
   <si>
@@ -1210,9 +1198,6 @@
     <t>Đại Cương, Kim Bảng, Hà Nam</t>
   </si>
   <si>
-    <t>20.636496060714716, 105.88530447418114</t>
-  </si>
-  <si>
     <t>Kho MML - Long An</t>
   </si>
   <si>
@@ -1363,15 +1348,6 @@
     <t>Thôn Vĩnh Sơn, Xã Vĩnh Hảo, Huyện Tuy Phong, Tỉnh Bình Thuận</t>
   </si>
   <si>
-    <t>11.3132444, 108.7534139</t>
-  </si>
-  <si>
-    <t>11.3132444</t>
-  </si>
-  <si>
-    <t>108.7534139</t>
-  </si>
-  <si>
     <t>Nhà máy Vĩnh Hảo B20L</t>
   </si>
   <si>
@@ -1525,15 +1501,6 @@
     <t>KCN Sông Hậu, Xã Đông Phú, Huyện Châu Thành, Hậu Giang</t>
   </si>
   <si>
-    <t>9.9610889, 105.8424</t>
-  </si>
-  <si>
-    <t>9.9610889</t>
-  </si>
-  <si>
-    <t>105.8424</t>
-  </si>
-  <si>
     <t>Nhà máy Hậu Giang Beer</t>
   </si>
   <si>
@@ -1585,15 +1552,6 @@
     <t>Số 7 VSIP II-A, Đường 31, Xã Vĩnh Tân, Thị Xã Tân Uyên, Bình Dương</t>
   </si>
   <si>
-    <t>11.1379247, 106.6978593</t>
-  </si>
-  <si>
-    <t>11.1379247</t>
-  </si>
-  <si>
-    <t>106.6978593</t>
-  </si>
-  <si>
     <t>Nhà máy gia công OCM tại Việt Nam</t>
   </si>
   <si>
@@ -1648,15 +1606,6 @@
     <t>Lô A19-20, KCN An Hiệp, xã Tường Đa, huyện Châu Thành, tỉnh Bến Tre</t>
   </si>
   <si>
-    <t>10.2797839, 106.3007738</t>
-  </si>
-  <si>
-    <t>10.2797839</t>
-  </si>
-  <si>
-    <t>106.3007738</t>
-  </si>
-  <si>
     <t>Nhà máy gia công tại Long An</t>
   </si>
   <si>
@@ -1693,6 +1642,27 @@
     <t xml:space="preserve"> 106.61395872263057</t>
   </si>
   <si>
+    <t>10.924485478734782, 106.77731002642267</t>
+  </si>
+  <si>
+    <t>10.924485478734782</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 106.77731002642267</t>
+  </si>
+  <si>
+    <t>Đồng Nai</t>
+  </si>
+  <si>
+    <t>10.905287321133404, 106.78710144342529</t>
+  </si>
+  <si>
+    <t>10.905287321133404</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 106.78710144342529</t>
+  </si>
+  <si>
     <t>10.889696291065894, 106.73420976703588</t>
   </si>
   <si>
@@ -1702,25 +1672,31 @@
     <t xml:space="preserve"> 106.73420976703588</t>
   </si>
   <si>
-    <t>10.924485478734782, 106.77731002642267</t>
-  </si>
-  <si>
-    <t>10.924485478734782</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 106.77731002642267</t>
-  </si>
-  <si>
-    <t>Đồng Nai</t>
-  </si>
-  <si>
-    <t>10.905287321133404, 106.78710144342529</t>
-  </si>
-  <si>
-    <t>10.905287321133404</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 106.78710144342529</t>
+    <t>DC NetCO</t>
+  </si>
+  <si>
+    <t>Hậu Giang Foods</t>
+  </si>
+  <si>
+    <t>9.966587120264782, 105.837811177831</t>
+  </si>
+  <si>
+    <t>9.966587120264782</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 105.837811177831</t>
+  </si>
+  <si>
+    <t>9.964086551571567, 105.84104034443797</t>
+  </si>
+  <si>
+    <t>9.964086551571567</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 105.84104034443797</t>
+  </si>
+  <si>
+    <t>11.277493342823563, 108.73517068109769</t>
   </si>
 </sst>
 </file>
@@ -3339,7 +3315,7 @@
         <v>251</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="D1" s="22" t="s">
         <v>252</v>
@@ -3395,16 +3371,16 @@
         <v>267</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>268</v>
+        <v>551</v>
       </c>
       <c r="J2" s="24">
         <v>6050</v>
       </c>
       <c r="K2" s="24">
-        <v>11.277082999999999</v>
+        <v>11.277493342823499</v>
       </c>
       <c r="L2" s="24">
-        <v>108.7345</v>
+        <v>108.735170681097</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -3412,28 +3388,28 @@
         <v>261</v>
       </c>
       <c r="B3" s="24" t="s">
+        <v>544</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="D3" s="24" t="s">
         <v>270</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="E3" s="24" t="s">
         <v>271</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>272</v>
       </c>
       <c r="F3" s="24">
         <v>8169001</v>
       </c>
       <c r="G3" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="H3" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="I3" s="24" t="s">
         <v>274</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>275</v>
       </c>
       <c r="J3" s="24">
         <v>4770</v>
@@ -3450,28 +3426,28 @@
         <v>261</v>
       </c>
       <c r="B4" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="D4" s="24" t="s">
         <v>277</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="E4" s="24" t="s">
         <v>278</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>279</v>
       </c>
       <c r="F4" s="24">
         <v>8156001</v>
       </c>
       <c r="G4" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="H4" s="24" t="s">
         <v>280</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="I4" s="24" t="s">
         <v>281</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>282</v>
       </c>
       <c r="J4" s="24">
         <v>3600</v>
@@ -3488,28 +3464,28 @@
         <v>261</v>
       </c>
       <c r="B5" s="24" t="s">
+        <v>543</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="E5" s="24" t="s">
         <v>284</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>286</v>
       </c>
       <c r="F5" s="24">
         <v>8167001</v>
       </c>
       <c r="G5" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" s="24" t="s">
         <v>287</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>289</v>
       </c>
       <c r="J5" s="24">
         <v>12943</v>
@@ -3526,28 +3502,28 @@
         <v>261</v>
       </c>
       <c r="B6" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="D6" s="24" t="s">
         <v>290</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="E6" s="24" t="s">
         <v>291</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>293</v>
       </c>
       <c r="F6" s="24">
         <v>8157001</v>
       </c>
       <c r="G6" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="I6" s="24" t="s">
         <v>294</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>296</v>
       </c>
       <c r="J6" s="24">
         <v>8196</v>
@@ -3564,28 +3540,28 @@
         <v>261</v>
       </c>
       <c r="B7" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>297</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="E7" s="24" t="s">
         <v>298</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>300</v>
       </c>
       <c r="F7" s="24">
         <v>8170001</v>
       </c>
       <c r="G7" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="I7" s="24" t="s">
         <v>301</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>303</v>
       </c>
       <c r="J7" s="24">
         <v>5880</v>
@@ -3602,28 +3578,28 @@
         <v>261</v>
       </c>
       <c r="B8" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="D8" s="24" t="s">
         <v>304</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="E8" s="24" t="s">
         <v>305</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>307</v>
       </c>
       <c r="F8" s="24">
         <v>8158001</v>
       </c>
       <c r="G8" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="I8" s="24" t="s">
         <v>308</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>310</v>
       </c>
       <c r="J8" s="24">
         <v>1000</v>
@@ -3640,28 +3616,28 @@
         <v>261</v>
       </c>
       <c r="B9" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" s="24" t="s">
         <v>311</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="E9" s="24" t="s">
         <v>312</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>314</v>
       </c>
       <c r="F9" s="24">
         <v>8159001</v>
       </c>
       <c r="G9" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="I9" s="24" t="s">
         <v>315</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>316</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>317</v>
       </c>
       <c r="J9" s="24">
         <v>6023.36</v>
@@ -3678,28 +3654,28 @@
         <v>261</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C10" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="E10" s="24" t="s">
         <v>312</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>314</v>
       </c>
       <c r="F10" s="24">
         <v>8159001</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J10" s="24">
         <v>15196</v>
@@ -3716,28 +3692,28 @@
         <v>261</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C11" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="E11" s="24" t="s">
         <v>312</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>314</v>
       </c>
       <c r="F11" s="24">
         <v>8159001</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J11" s="24">
         <v>5000</v>
@@ -3754,28 +3730,28 @@
         <v>261</v>
       </c>
       <c r="B12" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="D12" s="24" t="s">
         <v>324</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="E12" s="24" t="s">
         <v>325</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>326</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>327</v>
       </c>
       <c r="F12" s="24">
         <v>8160001</v>
       </c>
       <c r="G12" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="I12" s="24" t="s">
         <v>328</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>329</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>330</v>
       </c>
       <c r="J12" s="24">
         <v>15400</v>
@@ -3792,28 +3768,28 @@
         <v>261</v>
       </c>
       <c r="B13" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>331</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="E13" s="24" t="s">
         <v>332</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>333</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>334</v>
       </c>
       <c r="F13" s="24">
         <v>8161001</v>
       </c>
       <c r="G13" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>334</v>
+      </c>
+      <c r="I13" s="24" t="s">
         <v>335</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>336</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>337</v>
       </c>
       <c r="J13" s="24">
         <v>1000</v>
@@ -3830,28 +3806,28 @@
         <v>261</v>
       </c>
       <c r="B14" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="D14" s="24" t="s">
         <v>338</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="E14" s="24" t="s">
         <v>339</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>340</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>341</v>
       </c>
       <c r="F14" s="24">
         <v>8162001</v>
       </c>
       <c r="G14" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="I14" s="24" t="s">
         <v>341</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>343</v>
       </c>
       <c r="J14" s="24">
         <v>900</v>
@@ -3868,28 +3844,28 @@
         <v>261</v>
       </c>
       <c r="B15" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>344</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="E15" s="24" t="s">
         <v>345</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>347</v>
       </c>
       <c r="F15" s="24">
         <v>8164001</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J15" s="24">
         <v>20000</v>
@@ -3906,37 +3882,37 @@
         <v>261</v>
       </c>
       <c r="B16" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>350</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="E16" s="24" t="s">
         <v>351</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>352</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>353</v>
       </c>
       <c r="F16" s="24">
         <v>8163001</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="J16" s="24">
         <v>28984</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
@@ -3944,26 +3920,26 @@
         <v>261</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F17" s="24">
         <v>8165001</v>
       </c>
       <c r="G17" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="I17" s="24" t="s">
         <v>358</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>359</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>360</v>
       </c>
       <c r="J17" s="24">
         <v>730</v>
@@ -3980,37 +3956,37 @@
         <v>261</v>
       </c>
       <c r="B18" t="s">
+        <v>359</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>360</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>361</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="E18" s="24" t="s">
         <v>362</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>364</v>
       </c>
       <c r="F18" s="24">
         <v>8166001</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>547</v>
+        <v>530</v>
       </c>
       <c r="J18" s="24">
         <v>7700</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -4018,113 +3994,99 @@
         <v>261</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C19" s="24" t="s">
+        <v>360</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="E19" s="24" t="s">
         <v>362</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>364</v>
       </c>
       <c r="F19" s="24">
         <v>8166001</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>547</v>
-      </c>
-      <c r="J19" s="24">
-        <v>250</v>
-      </c>
-      <c r="K19" s="24" t="s">
-        <v>548</v>
-      </c>
-      <c r="L19" s="24" t="s">
-        <v>549</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="24" t="s">
         <v>261</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C20" s="24" t="s">
+        <v>360</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="E20" s="24" t="s">
         <v>362</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>364</v>
       </c>
       <c r="F20" s="24">
         <v>8166001</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>370</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>547</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="I20" s="24"/>
       <c r="J20" s="24">
         <v>570</v>
       </c>
-      <c r="K20" s="24" t="s">
-        <v>548</v>
-      </c>
-      <c r="L20" s="24" t="s">
-        <v>549</v>
-      </c>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="24" t="s">
         <v>261</v>
       </c>
       <c r="B21" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="D21" s="24" t="s">
         <v>371</v>
       </c>
-      <c r="C21" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>373</v>
-      </c>
       <c r="E21" s="24" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F21" s="24">
         <v>8171001</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="J21" s="24">
         <v>3850</v>
       </c>
       <c r="K21" s="24" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="L21" s="24" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -4132,33 +4094,33 @@
         <v>261</v>
       </c>
       <c r="B22" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>374</v>
+      </c>
+      <c r="D22" s="24" t="s">
         <v>375</v>
       </c>
-      <c r="C22" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>377</v>
-      </c>
       <c r="E22" s="24" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="24" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H22" s="24"/>
       <c r="I22" s="24" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="J22" s="24">
         <v>3850</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="L22" s="24" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
@@ -4166,30 +4128,24 @@
         <v>261</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="C23" s="24"/>
       <c r="D23" s="24" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="24" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>380</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>381</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="I23" s="24"/>
       <c r="J23" s="24"/>
-      <c r="K23" s="24">
-        <v>10.851160102363</v>
-      </c>
-      <c r="L23" s="24">
-        <v>106.95547296357</v>
-      </c>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="24" t="s">
@@ -4197,27 +4153,21 @@
       </c>
       <c r="B24" s="24"/>
       <c r="C24" s="24" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="24" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>384</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>385</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="I24" s="24"/>
       <c r="J24" s="24"/>
-      <c r="K24" s="24">
-        <v>10.919767850139401</v>
-      </c>
-      <c r="L24" s="24">
-        <v>106.859984357944</v>
-      </c>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="24" t="s">
@@ -4225,27 +4175,21 @@
       </c>
       <c r="B25" s="24"/>
       <c r="C25" s="24" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="24" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>388</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>389</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="I25" s="24"/>
       <c r="J25" s="24"/>
-      <c r="K25" s="24">
-        <v>20.636496060714698</v>
-      </c>
-      <c r="L25" s="24">
-        <v>105.885304474181</v>
-      </c>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="24" t="s">
@@ -4253,19 +4197,19 @@
       </c>
       <c r="B26" s="24"/>
       <c r="C26" s="24" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="24" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="J26" s="24"/>
       <c r="K26" s="24">
@@ -4277,692 +4221,682 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B27" s="24"/>
       <c r="C27" s="24" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
       <c r="G27" s="24" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="J27" s="24"/>
       <c r="K27" s="24" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="L27" s="24" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B28" s="24"/>
       <c r="C28" s="24" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24"/>
       <c r="F28" s="24"/>
       <c r="G28" s="24" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J28" s="24"/>
       <c r="K28" s="24" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="L28" s="24" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B29" s="24"/>
       <c r="C29" s="24" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24"/>
       <c r="F29" s="24"/>
       <c r="G29" s="24" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="J29" s="24"/>
       <c r="K29" s="24" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="L29" s="24" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B30" s="24"/>
       <c r="C30" s="24" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
       <c r="G30" s="24" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="I30" s="24" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J30" s="24"/>
       <c r="K30" s="24" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="L30" s="24" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B31" s="24"/>
       <c r="C31" s="24" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="24" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="J31" s="24"/>
       <c r="K31" s="24" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="24" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" s="24" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="J32" s="24"/>
       <c r="K32" s="24" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="L32" s="24" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B33" s="24"/>
       <c r="C33" s="24" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" s="24" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J33" s="24"/>
       <c r="K33" s="24" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="L33" s="24" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B34" s="24"/>
       <c r="C34" s="24" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
       <c r="F34" s="24"/>
       <c r="G34" s="24" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>440</v>
-      </c>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24" t="s">
-        <v>441</v>
-      </c>
-      <c r="L34" s="24" t="s">
-        <v>442</v>
+        <v>268</v>
+      </c>
+      <c r="J34" s="24">
+        <v>6050</v>
+      </c>
+      <c r="K34" s="24">
+        <v>11.277082999999999</v>
+      </c>
+      <c r="L34" s="24">
+        <v>108.7345</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B35" s="24"/>
       <c r="C35" s="24" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
       <c r="G35" s="24" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>439</v>
-      </c>
-      <c r="I35" s="24" t="s">
-        <v>440</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="I35" s="24"/>
       <c r="J35" s="24"/>
-      <c r="K35" s="24" t="s">
-        <v>441</v>
-      </c>
-      <c r="L35" s="24" t="s">
-        <v>442</v>
-      </c>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="24"/>
       <c r="F36" s="24"/>
       <c r="G36" s="24" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I36" s="24" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="J36" s="24"/>
       <c r="K36" s="24" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="L36" s="24" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B37" s="24"/>
       <c r="C37" s="24" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="D37" s="24"/>
       <c r="E37" s="24"/>
       <c r="F37" s="24"/>
       <c r="G37" s="24" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="I37" s="24" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="J37" s="24"/>
       <c r="K37" s="24" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="L37" s="24" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B38" s="24"/>
       <c r="C38" s="24" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="D38" s="24"/>
       <c r="E38" s="24"/>
       <c r="F38" s="24"/>
       <c r="G38" s="24" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="J38" s="24"/>
       <c r="K38" s="24" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="L38" s="24" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B39" s="24"/>
       <c r="C39" s="24" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24"/>
       <c r="F39" s="24"/>
       <c r="G39" s="24" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="I39" s="24" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="J39" s="24"/>
       <c r="K39" s="24" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="L39" s="24" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B40" s="24"/>
       <c r="C40" s="24" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
       <c r="F40" s="24"/>
       <c r="G40" s="24" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="J40" s="24"/>
       <c r="K40" s="24" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="L40" s="24" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B41" s="24"/>
       <c r="C41" s="24" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
       <c r="F41" s="24"/>
       <c r="G41" s="24" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="J41" s="24"/>
       <c r="K41" s="24" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="L41" s="24" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B42" s="24"/>
       <c r="C42" s="24" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="D42" s="24"/>
       <c r="E42" s="24"/>
       <c r="F42" s="24"/>
       <c r="G42" s="24" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="J42" s="24"/>
       <c r="K42" s="24" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B43" s="24"/>
       <c r="C43" s="24" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D43" s="24"/>
       <c r="E43" s="24"/>
       <c r="F43" s="24"/>
       <c r="G43" s="24" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="J43" s="24"/>
       <c r="K43" s="24" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="L43" s="24" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B44" s="24"/>
       <c r="C44" s="24" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="24"/>
       <c r="F44" s="24"/>
       <c r="G44" s="24" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="I44" s="24" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="J44" s="24"/>
       <c r="K44" s="24" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="L44" s="24" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B45" s="24"/>
       <c r="C45" s="24" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="D45" s="24"/>
       <c r="E45" s="24"/>
       <c r="F45" s="24"/>
       <c r="G45" s="24" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="I45" s="24" t="s">
-        <v>494</v>
+        <v>545</v>
       </c>
       <c r="J45" s="24"/>
       <c r="K45" s="24" t="s">
-        <v>495</v>
+        <v>546</v>
       </c>
       <c r="L45" s="24" t="s">
-        <v>496</v>
+        <v>547</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B46" s="24"/>
       <c r="C46" s="24" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="D46" s="24"/>
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
       <c r="G46" s="24" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>494</v>
+        <v>548</v>
       </c>
       <c r="J46" s="24"/>
       <c r="K46" s="24" t="s">
-        <v>495</v>
+        <v>549</v>
       </c>
       <c r="L46" s="24" t="s">
-        <v>496</v>
+        <v>550</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B47" s="24"/>
       <c r="C47" s="24" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D47" s="24"/>
       <c r="E47" s="24"/>
       <c r="F47" s="24"/>
       <c r="G47" s="24" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="J47" s="24"/>
       <c r="K47" s="24" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="L47" s="24" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="24" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="24"/>
       <c r="F48" s="24"/>
       <c r="G48" s="24" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="J48" s="24"/>
       <c r="K48" s="24" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="L48" s="24" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B49" s="24"/>
       <c r="C49" s="24" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="D49" s="24"/>
       <c r="E49" s="24"/>
       <c r="F49" s="24"/>
       <c r="G49" s="24" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>513</v>
-      </c>
-      <c r="I49" s="24" t="s">
-        <v>514</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="I49" s="24"/>
       <c r="J49" s="24"/>
-      <c r="K49" s="24" t="s">
-        <v>515</v>
-      </c>
-      <c r="L49" s="24" t="s">
-        <v>516</v>
-      </c>
+      <c r="K49" s="24"/>
+      <c r="L49" s="24"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B50" s="24"/>
       <c r="C50" s="24" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="D50" s="24"/>
       <c r="E50" s="24"/>
       <c r="F50" s="24"/>
       <c r="G50" s="24" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="J50" s="24"/>
       <c r="K50" s="24" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="L50" s="24" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B51" s="24"/>
       <c r="C51" s="24" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="D51" s="24"/>
       <c r="E51" s="24"/>
       <c r="F51" s="24"/>
       <c r="G51" s="24" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="I51" s="24"/>
       <c r="J51" s="24"/>
@@ -4971,86 +4905,80 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B52" s="24"/>
       <c r="C52" s="24" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="D52" s="24"/>
       <c r="E52" s="24"/>
       <c r="F52" s="24"/>
       <c r="G52" s="24" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="J52" s="24"/>
       <c r="K52" s="24" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="L52" s="24" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B53" s="24"/>
       <c r="C53" s="24" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="D53" s="24"/>
       <c r="E53" s="24"/>
       <c r="F53" s="24"/>
       <c r="G53" s="24" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>534</v>
-      </c>
-      <c r="I53" s="24" t="s">
-        <v>535</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="I53" s="24"/>
       <c r="J53" s="24"/>
-      <c r="K53" s="24" t="s">
-        <v>536</v>
-      </c>
-      <c r="L53" s="24" t="s">
-        <v>537</v>
-      </c>
+      <c r="K53" s="24"/>
+      <c r="L53" s="24"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="24" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B54" s="24"/>
       <c r="C54" s="24" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="D54" s="24"/>
       <c r="E54" s="24"/>
       <c r="F54" s="24"/>
       <c r="G54" s="24" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="J54" s="24"/>
       <c r="K54" s="24" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="L54" s="24" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
